--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484017_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484017_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9239</v>
+        <v>2.6724</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1523</v>
+        <v>0.6242</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0762</v>
+        <v>2.0482</v>
       </c>
       <c r="G2" t="n">
         <v>2.2245</v>
@@ -610,13 +610,13 @@
         <v>3.1741</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3167</v>
+        <v>-0.5683</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9635</v>
+        <v>-0.1869</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3533</v>
+        <v>-0.3813</v>
       </c>
       <c r="V2" t="n">
         <v>1.8097</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2954</v>
+        <v>1.4545</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4482</v>
+        <v>1.3268</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1528</v>
+        <v>0.1278</v>
       </c>
       <c r="G3" t="n">
         <v>0.3866</v>
@@ -688,13 +688,13 @@
         <v>3.1741</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.5393</v>
+        <v>-1.3802</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8161</v>
+        <v>0.0625</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.7233</v>
+        <v>-1.4427</v>
       </c>
       <c r="V3" t="n">
         <v>0.266</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0531</v>
+        <v>-0.177</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3364</v>
+        <v>-0.3761</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2833</v>
+        <v>0.1991</v>
       </c>
       <c r="G4" t="n">
         <v>-1.1869</v>
@@ -766,13 +766,13 @@
         <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4019</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4025</v>
+        <v>0.3628</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8044</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="V4" t="n">
         <v>0.9405</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.6818</v>
+        <v>-0.3604</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8209</v>
+        <v>-0.1067</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1391</v>
+        <v>-0.2537</v>
       </c>
       <c r="G5" t="n">
         <v>1.1243</v>
@@ -844,13 +844,13 @@
         <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4887</v>
+        <v>-0.1672</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.391</v>
+        <v>0.3232</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0977</v>
+        <v>-0.4904</v>
       </c>
       <c r="V5" t="n">
         <v>0.0713</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. OLAGUIBE GONZALEZ</t>
+          <t>P. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9535</v>
+        <v>-2.1016</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8163</v>
+        <v>-2.2596</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8628</v>
+        <v>0.158</v>
       </c>
       <c r="G6" t="n">
+        <v>-0.8431999999999999</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-1.3964</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.5532</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0.5365</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.5391</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.3067</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.8574000000000001</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.5507</v>
       </c>
-      <c r="H6" t="n">
-        <v>0.4081</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.1425</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1.3837</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1.2606</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="M6" t="n">
-        <v>-0.833</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.8525</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.0195</v>
-      </c>
       <c r="P6" t="n">
-        <v>-3.3725</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.9596</v>
+        <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5871</v>
+        <v>1.3887</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8683999999999999</v>
+        <v>-0.6632</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.2608</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1087</v>
+        <v>-0.924</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MORENO MARTIN</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1843</v>
+        <v>-2.4582</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1178</v>
+        <v>-1.7367</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0665</v>
+        <v>-0.7215</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.2183</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3964</v>
+        <v>1.0126</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5532</v>
+        <v>-1.2309</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5365</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5391</v>
+        <v>2.2634</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0026</v>
+        <v>-1.3929</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3067</v>
+        <v>-1.0888</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.2508</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5507</v>
+        <v>0.162</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7459</v>
+        <v>-1.4978</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4025</v>
+        <v>0.0511</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1484</v>
+        <v>-1.5489</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9405</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DIEZ VALERO</t>
+          <t>H. OLAGUIBE GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.211</v>
+        <v>-2.632</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3638</v>
+        <v>-3.3265</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1527</v>
+        <v>0.6945</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.677</v>
+        <v>0.5507</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1237</v>
+        <v>0.4081</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5532</v>
+        <v>0.1425</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3291</v>
+        <v>1.3837</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4171</v>
+        <v>1.2606</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.123</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3479</v>
+        <v>-0.833</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7067</v>
+        <v>-0.8525</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6412</v>
+        <v>0.0195</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7855</v>
+        <v>-3.3725</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.9677</v>
+        <v>-4.9596</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1822</v>
+        <v>1.5871</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5174</v>
+        <v>0.1899</v>
       </c>
       <c r="T8" t="n">
-        <v>1.933</v>
+        <v>0.2495</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4156</v>
+        <v>-0.0596</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>A. DIEZ VALERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6149</v>
+        <v>-3.5655</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6971</v>
+        <v>-3.6902</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9179</v>
+        <v>0.1247</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2183</v>
+        <v>-1.677</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0126</v>
+        <v>-1.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2309</v>
+        <v>-0.5532</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8705000000000001</v>
+        <v>-0.3291</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2634</v>
+        <v>-0.4171</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3929</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0888</v>
+        <v>-1.3479</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2508</v>
+        <v>-0.7067</v>
       </c>
       <c r="O9" t="n">
-        <v>0.162</v>
+        <v>-0.6412</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1984</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9838</v>
+        <v>-3.9677</v>
       </c>
       <c r="R9" t="n">
         <v>2.1822</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6545</v>
+        <v>0.1629</v>
       </c>
       <c r="T9" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.6066</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.7453</v>
+        <v>-0.4437</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9405</v>
+        <v>-0.266</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6745</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>-0.266</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.479299999999999</v>
+        <v>-7.167800000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.856400000000001</v>
+        <v>-9.5448</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3769</v>
+        <v>2.3771</v>
       </c>
       <c r="G10" t="n">
         <v>0.3606999999999996</v>
@@ -1234,13 +1234,13 @@
         <v>16.8626</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.7612</v>
+        <v>-4.4496</v>
       </c>
       <c r="T10" t="n">
-        <v>1.4178</v>
+        <v>1.7296</v>
       </c>
       <c r="U10" t="n">
-        <v>-6.1793</v>
+        <v>-6.1792</v>
       </c>
       <c r="V10" t="n">
         <v>1.881</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ALMENTA MACIAS</t>
+          <t>R. VICENTE SIMO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.7712</v>
+        <v>5.5277</v>
       </c>
       <c r="E11" t="n">
-        <v>4.8177</v>
+        <v>3.4853</v>
       </c>
       <c r="F11" t="n">
-        <v>2.9535</v>
+        <v>2.0424</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0946</v>
+        <v>1.6337</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2086</v>
+        <v>-0.3886</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1141</v>
+        <v>2.0222</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5162</v>
+        <v>3.1143</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9955</v>
+        <v>0.3279</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4794</v>
+        <v>2.7865</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4216</v>
+        <v>-1.4807</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7869</v>
+        <v>-0.7165</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6347</v>
+        <v>-0.7642</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5952</v>
+        <v>2.7774</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R11" t="n">
-        <v>3.5709</v>
+        <v>3.7693</v>
       </c>
       <c r="S11" t="n">
-        <v>6.0815</v>
+        <v>1.1166</v>
       </c>
       <c r="T11" t="n">
-        <v>5.9518</v>
+        <v>0.7597</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1297</v>
+        <v>0.357</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6745</v>
+        <v>0.6032</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6745</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.4504</v>
+        <v>5.1306</v>
       </c>
       <c r="E12" t="n">
         <v>3.1538</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2966</v>
+        <v>1.9768</v>
       </c>
       <c r="G12" t="n">
         <v>1.8058</v>
@@ -1390,13 +1390,13 @@
         <v>3.7693</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4705</v>
+        <v>1.1507</v>
       </c>
       <c r="T12" t="n">
         <v>1.0658</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5953000000000001</v>
+        <v>0.0849</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6032</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. IDDRISU</t>
+          <t>A. ALMENTA MACIAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9317</v>
+        <v>4.5139</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8441</v>
+        <v>1.3487</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0877</v>
+        <v>3.1652</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.034</v>
+        <v>1.0946</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1719</v>
+        <v>2.2086</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2059</v>
+        <v>-1.1141</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1416</v>
+        <v>2.5162</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2982</v>
+        <v>2.9955</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8434</v>
+        <v>-0.4794</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1756</v>
+        <v>-1.4216</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1263</v>
+        <v>-0.7869</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0493</v>
+        <v>-0.6347</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7855</v>
+        <v>3.5709</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9658</v>
+        <v>2.8242</v>
       </c>
       <c r="T13" t="n">
-        <v>2.222</v>
+        <v>2.4828</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2562</v>
+        <v>0.3414</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4724</v>
+        <v>-0.6745</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. VICENTE SIMO</t>
+          <t>J. GONZALEZ LOPEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.113</v>
+        <v>3.6839</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7508</v>
+        <v>1.8253</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3622</v>
+        <v>1.8586</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6337</v>
+        <v>3.0792</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3886</v>
+        <v>0.7615</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0222</v>
+        <v>2.3178</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1143</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3279</v>
+        <v>1.1598</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7865</v>
+        <v>1.8901</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4807</v>
+        <v>0.0293</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7165</v>
+        <v>-0.3983</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7642</v>
+        <v>0.4276</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7774</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R14" t="n">
-        <v>3.7693</v>
+        <v>1.7855</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.298</v>
+        <v>0.5371</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9748</v>
+        <v>0.4932</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3232</v>
+        <v>0.0439</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6032</v>
+        <v>0.266</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GONZALEZ LOPEZ</t>
+          <t>A. IDDRISU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9536</v>
+        <v>3.5899</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7233</v>
+        <v>2.9258</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2303</v>
+        <v>0.6641</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0792</v>
+        <v>-0.034</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7615</v>
+        <v>0.1719</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3178</v>
+        <v>-0.2059</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>1.1416</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1598</v>
+        <v>0.2982</v>
       </c>
       <c r="L15" t="n">
-        <v>1.8901</v>
+        <v>0.8434</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0293</v>
+        <v>-1.1756</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3983</v>
+        <v>-0.1263</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4276</v>
+        <v>-1.0493</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
         <v>1.7855</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1933</v>
+        <v>1.624</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3912</v>
+        <v>1.3038</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5844</v>
+        <v>0.3202</v>
       </c>
       <c r="V15" t="n">
-        <v>0.266</v>
+        <v>1.2065</v>
       </c>
       <c r="W15" t="n">
-        <v>0.266</v>
+        <v>1.4724</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8337</v>
+        <v>-0.6296</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2111</v>
+        <v>-0.007</v>
       </c>
       <c r="F16" t="n">
         <v>-0.6226</v>
@@ -1702,10 +1702,10 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.136</v>
+        <v>0.068</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3117</v>
+        <v>-0.1077</v>
       </c>
       <c r="U16" t="n">
         <v>0.1757</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9332</v>
+        <v>-0.6952</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.4671</v>
+        <v>-2.1407</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5339</v>
+        <v>1.4455</v>
       </c>
       <c r="G17" t="n">
         <v>-1.313</v>
@@ -1780,13 +1780,13 @@
         <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5407999999999999</v>
+        <v>0.6972</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0599</v>
+        <v>0.2665</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5191</v>
+        <v>0.4307</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6745</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. AGUILERA MELCHOR</t>
+          <t>B. MARTINEZ JANER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.6147</v>
+        <v>-3.1174</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.3884</v>
+        <v>-5.5598</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2263</v>
+        <v>2.4424</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2864</v>
+        <v>-1.2682</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7889</v>
+        <v>-0.4584</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4975</v>
+        <v>-0.8097</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.9601</v>
+        <v>-1.0877</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3201</v>
+        <v>0.2727</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.64</v>
+        <v>-1.3604</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3263</v>
+        <v>-0.1805</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4688</v>
+        <v>-0.7311</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1425</v>
+        <v>0.5507</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1984</v>
+        <v>-1.5871</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7935</v>
+        <v>2.3806</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2607</v>
+        <v>-0.2621</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4364</v>
+        <v>-0.5044</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1757</v>
+        <v>0.2423</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. MARTINEZ JANER</t>
+          <t>A. AGUILERA MELCHOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6436</v>
+        <v>-3.2066</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.8659</v>
+        <v>-2.9803</v>
       </c>
       <c r="F19" t="n">
-        <v>2.2222</v>
+        <v>-0.2263</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2682</v>
+        <v>-2.2864</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4584</v>
+        <v>-1.7889</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8097</v>
+        <v>-0.4975</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0877</v>
+        <v>-1.9601</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2727</v>
+        <v>-1.3201</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3604</v>
+        <v>-0.64</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1805</v>
+        <v>-0.3263</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7311</v>
+        <v>-0.4688</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5507</v>
+        <v>0.1425</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5871</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.9677</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3806</v>
+        <v>0.7935</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7884</v>
+        <v>0.1474</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8105</v>
+        <v>-0.0283</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0221</v>
+        <v>0.1757</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.7152</v>
+        <v>-3.9168</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.7342</v>
+        <v>-4.4281</v>
       </c>
       <c r="F20" t="n">
-        <v>0.019</v>
+        <v>0.5113</v>
       </c>
       <c r="G20" t="n">
         <v>-3.1842</v>
@@ -2014,13 +2014,13 @@
         <v>0.9919</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.539</v>
+        <v>0.2593</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1418</v>
+        <v>0.4479</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6808</v>
+        <v>-0.1885</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,22 +2047,22 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>7.479500000000001</v>
+        <v>10.8804</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.376999999999998</v>
+        <v>-2.376999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>9.856499999999999</v>
+        <v>13.2574</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3605000000000005</v>
+        <v>-0.3605000000000009</v>
       </c>
       <c r="H21" t="n">
         <v>0.9347999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.295399999999999</v>
+        <v>-1.2954</v>
       </c>
       <c r="J21" t="n">
         <v>7.3138</v>
@@ -2083,7 +2083,7 @@
         <v>-2.4283</v>
       </c>
       <c r="P21" t="n">
-        <v>4.959700000000001</v>
+        <v>4.9597</v>
       </c>
       <c r="Q21" t="n">
         <v>-16.8625</v>
@@ -2092,19 +2092,19 @@
         <v>21.8223</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7616</v>
+        <v>8.162400000000002</v>
       </c>
       <c r="T21" t="n">
         <v>6.1793</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4176</v>
+        <v>1.9833</v>
       </c>
       <c r="V21" t="n">
         <v>-1.8809</v>
       </c>
       <c r="W21" t="n">
-        <v>0.9925999999999996</v>
+        <v>0.9925999999999999</v>
       </c>
       <c r="X21" t="n">
         <v>-2.8736</v>
